--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1071,30 +1071,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>target_world</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>reward_crystal</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>icon_res</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sort</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>name[language]</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>description[language_1]</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1123,30 +1128,35 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1175,30 +1185,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>附加参数2(类型3=征服世界id 0=无)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>奖励-魔晶</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>图标资源</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1218,23 +1233,26 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>101</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4001001</v>
       </c>
       <c r="I4" t="n">
         <v>4001001</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>4001001</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>击杀生物10只</t>
         </is>
@@ -1254,23 +1272,26 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>50</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>102</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4001003</v>
       </c>
       <c r="I5" t="n">
         <v>4001003</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>4001003</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>击杀生物100只</t>
         </is>
@@ -1290,23 +1311,26 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>200</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>103</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4001005</v>
       </c>
       <c r="I6" t="n">
         <v>4001005</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>4001005</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>击杀生物1000只</t>
         </is>
@@ -1326,23 +1350,26 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>500</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>104</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4001007</v>
       </c>
       <c r="I7" t="n">
         <v>4001007</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>4001007</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>击杀生物10000只</t>
         </is>
@@ -1362,23 +1389,26 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>1000</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>105</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4001009</v>
       </c>
       <c r="I8" t="n">
         <v>4001009</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>4001009</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>击杀生物100000只</t>
         </is>
@@ -1398,23 +1428,26 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>5000</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ui_achievement_kill</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>106</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4001011</v>
       </c>
       <c r="I9" t="n">
         <v>4001011</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>4001011</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>击杀生物1000000只</t>
         </is>
@@ -1434,23 +1467,26 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>10</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>201</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4002001</v>
       </c>
       <c r="I10" t="n">
         <v>4002001</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>4002001</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>游玩时间1小时</t>
         </is>
@@ -1470,23 +1506,26 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>202</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4002003</v>
       </c>
       <c r="I11" t="n">
         <v>4002003</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>4002003</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>游玩时间2小时</t>
         </is>
@@ -1506,23 +1545,26 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>100</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>203</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4002005</v>
       </c>
       <c r="I12" t="n">
         <v>4002005</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>4002005</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>游玩时间3小时</t>
         </is>
@@ -1542,23 +1584,26 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>150</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>204</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4002007</v>
       </c>
       <c r="I13" t="n">
         <v>4002007</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>4002007</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>游玩时间4小时</t>
         </is>
@@ -1578,23 +1623,26 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>200</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>205</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4002009</v>
       </c>
       <c r="I14" t="n">
         <v>4002009</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>4002009</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>游玩时间5小时</t>
         </is>
@@ -1614,23 +1662,26 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>250</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>206</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4002011</v>
       </c>
       <c r="I15" t="n">
         <v>4002011</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>4002011</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>游玩时间6小时</t>
         </is>
@@ -1650,23 +1701,26 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>300</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>207</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4002013</v>
       </c>
       <c r="I16" t="n">
         <v>4002013</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>4002013</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>游玩时间7小时</t>
         </is>
@@ -1686,23 +1740,26 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>350</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>208</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4002015</v>
       </c>
       <c r="I17" t="n">
         <v>4002015</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>4002015</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>游玩时间8小时</t>
         </is>
@@ -1722,23 +1779,26 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>400</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>209</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4002017</v>
       </c>
       <c r="I18" t="n">
         <v>4002017</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>4002017</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>游玩时间9小时</t>
         </is>
@@ -1758,23 +1818,26 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>450</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ui_achievement_time</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>210</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4002019</v>
       </c>
       <c r="I19" t="n">
         <v>4002019</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>4002019</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>游玩时间10小时</t>
         </is>
@@ -1794,23 +1857,26 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>200</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>301</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4003101</v>
       </c>
       <c r="I20" t="n">
         <v>4003101</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>4003101</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>难度1通关1次</t>
         </is>
@@ -1830,23 +1896,26 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
         <v>500</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>302</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4003103</v>
       </c>
       <c r="I21" t="n">
         <v>4003103</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>4003103</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>难度1通关10次</t>
         </is>
@@ -1866,23 +1935,26 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>1000</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>303</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4003105</v>
       </c>
       <c r="I22" t="n">
         <v>4003105</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>4003105</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>难度1通关100次</t>
         </is>
@@ -1902,23 +1974,26 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
         <v>200</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>304</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4003201</v>
       </c>
       <c r="I23" t="n">
         <v>4003201</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>4003201</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>难度2通关1次</t>
         </is>
@@ -1938,23 +2013,26 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
         <v>500</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>305</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4003203</v>
       </c>
       <c r="I24" t="n">
         <v>4003203</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>4003203</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>难度2通关10次</t>
         </is>
@@ -1974,23 +2052,26 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
         <v>1000</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>306</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4003205</v>
       </c>
       <c r="I25" t="n">
         <v>4003205</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>4003205</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>难度2通关100次</t>
         </is>
@@ -2010,23 +2091,26 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
         <v>200</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>307</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4003301</v>
       </c>
       <c r="I26" t="n">
         <v>4003301</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>4003301</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>难度3通关1次</t>
         </is>
@@ -2046,23 +2130,26 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>500</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>308</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4003303</v>
       </c>
       <c r="I27" t="n">
         <v>4003303</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>4003303</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>难度3通关10次</t>
         </is>
@@ -2082,23 +2169,26 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
         <v>1000</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>309</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4003305</v>
       </c>
       <c r="I28" t="n">
         <v>4003305</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>4003305</v>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>难度3通关100次</t>
         </is>
@@ -2118,23 +2208,26 @@
         <v>4</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
         <v>200</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>310</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4003401</v>
       </c>
       <c r="I29" t="n">
         <v>4003401</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>4003401</v>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>难度4通关1次</t>
         </is>
@@ -2154,23 +2247,26 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
         <v>500</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>311</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4003403</v>
       </c>
       <c r="I30" t="n">
         <v>4003403</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>4003403</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>难度4通关10次</t>
         </is>
@@ -2190,23 +2286,26 @@
         <v>4</v>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
         <v>1000</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>312</v>
-      </c>
-      <c r="H31" t="n">
-        <v>4003405</v>
       </c>
       <c r="I31" t="n">
         <v>4003405</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>4003405</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>难度4通关100次</t>
         </is>
@@ -2226,23 +2325,26 @@
         <v>5</v>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
         <v>200</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>313</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4003501</v>
       </c>
       <c r="I32" t="n">
         <v>4003501</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="n">
+        <v>4003501</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>难度5通关1次</t>
         </is>
@@ -2262,23 +2364,26 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
         <v>500</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>314</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4003503</v>
       </c>
       <c r="I33" t="n">
         <v>4003503</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>4003503</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>难度5通关10次</t>
         </is>
@@ -2298,23 +2403,26 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
         <v>1000</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>315</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4003505</v>
       </c>
       <c r="I34" t="n">
         <v>4003505</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>4003505</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>难度5通关100次</t>
         </is>
@@ -2334,23 +2442,26 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
         <v>200</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>316</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4003601</v>
       </c>
       <c r="I35" t="n">
         <v>4003601</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>4003601</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>难度6通关1次</t>
         </is>
@@ -2370,23 +2481,26 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
         <v>500</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>317</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4003603</v>
       </c>
       <c r="I36" t="n">
         <v>4003603</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="n">
+        <v>4003603</v>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>难度6通关10次</t>
         </is>
@@ -2406,23 +2520,26 @@
         <v>6</v>
       </c>
       <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
         <v>1000</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>318</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4003605</v>
       </c>
       <c r="I37" t="n">
         <v>4003605</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="n">
+        <v>4003605</v>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>难度6通关100次</t>
         </is>
@@ -2442,23 +2559,26 @@
         <v>7</v>
       </c>
       <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
         <v>200</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>319</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4003701</v>
       </c>
       <c r="I38" t="n">
         <v>4003701</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>4003701</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>难度7通关1次</t>
         </is>
@@ -2478,23 +2598,26 @@
         <v>7</v>
       </c>
       <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
         <v>500</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>320</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4003703</v>
       </c>
       <c r="I39" t="n">
         <v>4003703</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>4003703</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>难度7通关10次</t>
         </is>
@@ -2514,23 +2637,26 @@
         <v>7</v>
       </c>
       <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
         <v>1000</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>321</v>
-      </c>
-      <c r="H40" t="n">
-        <v>4003705</v>
       </c>
       <c r="I40" t="n">
         <v>4003705</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="n">
+        <v>4003705</v>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>难度7通关100次</t>
         </is>
@@ -2550,23 +2676,26 @@
         <v>8</v>
       </c>
       <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
         <v>200</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>322</v>
-      </c>
-      <c r="H41" t="n">
-        <v>4003801</v>
       </c>
       <c r="I41" t="n">
         <v>4003801</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>4003801</v>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>难度8通关1次</t>
         </is>
@@ -2586,23 +2715,26 @@
         <v>8</v>
       </c>
       <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
         <v>500</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>323</v>
-      </c>
-      <c r="H42" t="n">
-        <v>4003803</v>
       </c>
       <c r="I42" t="n">
         <v>4003803</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="n">
+        <v>4003803</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>难度8通关10次</t>
         </is>
@@ -2622,23 +2754,26 @@
         <v>8</v>
       </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
         <v>1000</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>324</v>
-      </c>
-      <c r="H43" t="n">
-        <v>4003805</v>
       </c>
       <c r="I43" t="n">
         <v>4003805</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="n">
+        <v>4003805</v>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>难度8通关100次</t>
         </is>
@@ -2658,23 +2793,26 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
         <v>200</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>325</v>
-      </c>
-      <c r="H44" t="n">
-        <v>4003901</v>
       </c>
       <c r="I44" t="n">
         <v>4003901</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="n">
+        <v>4003901</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>难度9通关1次</t>
         </is>
@@ -2694,23 +2832,26 @@
         <v>9</v>
       </c>
       <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>500</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>326</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4003903</v>
       </c>
       <c r="I45" t="n">
         <v>4003903</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>4003903</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>难度9通关10次</t>
         </is>
@@ -2730,23 +2871,26 @@
         <v>9</v>
       </c>
       <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
         <v>1000</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>327</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4003905</v>
       </c>
       <c r="I46" t="n">
         <v>4003905</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="n">
+        <v>4003905</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>难度9通关100次</t>
         </is>
@@ -2766,23 +2910,26 @@
         <v>10</v>
       </c>
       <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
         <v>200</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>328</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4003001</v>
       </c>
       <c r="I47" t="n">
         <v>4003001</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" t="n">
+        <v>4003001</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>难度10通关1次</t>
         </is>
@@ -2802,23 +2949,26 @@
         <v>10</v>
       </c>
       <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
         <v>500</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>329</v>
-      </c>
-      <c r="H48" t="n">
-        <v>4003003</v>
       </c>
       <c r="I48" t="n">
         <v>4003003</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="n">
+        <v>4003003</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>难度10通关10次</t>
         </is>
@@ -2838,23 +2988,26 @@
         <v>10</v>
       </c>
       <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
         <v>1000</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>ui_achievement_conquer</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>330</v>
-      </c>
-      <c r="H49" t="n">
-        <v>4003005</v>
       </c>
       <c r="I49" t="n">
         <v>4003005</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="n">
+        <v>4003005</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>难度10通关100次</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_kill,Achievement</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_time,Achievement</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ui_research_16,Research</t>
+          <t>ui_achievement_clear,Achievement</t>
         </is>
       </c>
       <c r="H15" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3600,7200,10800,14400,18000,21600,25200,28800,32400,36000</t>
+          <t>3600,18000,36000,72000,180000,360000,720000,1080000,1440000,1800000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20.75" customWidth="1" min="2" max="2"/>
@@ -1219,412 +1219,412 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100001</v>
+        <v>51000</v>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10,100,1000,10000,100000,1000000</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10,50,200,500,1000,5000</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ui_achievement_kill,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="I4" t="n">
-        <v>4001001</v>
+        <v>4005001</v>
       </c>
       <c r="J4" t="n">
-        <v>4001001</v>
+        <v>4005001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>击杀生物(6级)</t>
+          <t>孕育人类魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>200001</v>
+        <v>52000</v>
       </c>
       <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
         <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3600,18000,36000,72000,180000,360000,720000,1080000,1440000,1800000</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10,50,100,150,200,250,300,350,400,450</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ui_achievement_time,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="I5" t="n">
-        <v>4002001</v>
+        <v>4005002</v>
       </c>
       <c r="J5" t="n">
-        <v>4002001</v>
+        <v>4005002</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>游玩时间(10级)</t>
+          <t>孕育骷髅魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>301001</v>
+        <v>53000</v>
       </c>
       <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100,500,2500,</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>301</v>
+        <v>503</v>
       </c>
       <c r="I6" t="n">
-        <v>4003101</v>
+        <v>4005003</v>
       </c>
       <c r="J6" t="n">
-        <v>4003101</v>
+        <v>4005003</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>难度1通关(3级)</t>
+          <t>孕育史莱姆魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>302001</v>
+        <v>54000</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>200,1000,5000,</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>304</v>
+        <v>504</v>
       </c>
       <c r="I7" t="n">
-        <v>4003201</v>
+        <v>4005004</v>
       </c>
       <c r="J7" t="n">
-        <v>4003201</v>
+        <v>4005004</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>难度2通关(3级)</t>
+          <t>孕育魅魔魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>303001</v>
+        <v>55000</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>300,1500,7500,</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>307</v>
+        <v>505</v>
       </c>
       <c r="I8" t="n">
-        <v>4003301</v>
+        <v>4005005</v>
       </c>
       <c r="J8" t="n">
-        <v>4003301</v>
+        <v>4005005</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>难度3通关(3级)</t>
+          <t>孕育牛头人魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>304001</v>
+        <v>56000</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>400,2000,10000,</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>310</v>
+        <v>506</v>
       </c>
       <c r="I9" t="n">
-        <v>4003401</v>
+        <v>4005006</v>
       </c>
       <c r="J9" t="n">
-        <v>4003401</v>
+        <v>4005006</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>难度4通关(3级)</t>
+          <t>孕育哥布林魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>305001</v>
+        <v>57000</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>500,2500,12500,</t>
+          <t>20,100,200,1000,2000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_45,Achievement</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>313</v>
+        <v>507</v>
       </c>
       <c r="I10" t="n">
-        <v>4003501</v>
+        <v>4005007</v>
       </c>
       <c r="J10" t="n">
-        <v>4003501</v>
+        <v>4005007</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>难度5通关(3级)</t>
+          <t>孕育兽人魔物次数(5级)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>306001</v>
+        <v>100001</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>10,100,1000,10000,100000,1000000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>600,3000,15000,</t>
+          <t>10,50,200,500,1000,5000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_kill,Achievement</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>316</v>
+        <v>101</v>
       </c>
       <c r="I11" t="n">
-        <v>4003601</v>
+        <v>4001001</v>
       </c>
       <c r="J11" t="n">
-        <v>4003601</v>
+        <v>4001001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>难度6通关(3级)</t>
+          <t>击杀生物(6级)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>307001</v>
+        <v>200001</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>3600,18000,36000,72000,180000,360000,720000,1080000,1440000,1800000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>700,3500,17500,</t>
+          <t>10,50,100,150,200,250,300,350,400,450</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ui_achievement_clear,Achievement</t>
+          <t>ui_achievement_time,Achievement</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="I12" t="n">
-        <v>4003701</v>
+        <v>4002001</v>
       </c>
       <c r="J12" t="n">
-        <v>4003701</v>
+        <v>4002001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>难度7通关(3级)</t>
+          <t>游玩时间(10级)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>308001</v>
+        <v>301001</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,10,100,1000,10000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>800,4000,20000,</t>
+          <t>100,500,1000,5000,10000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1633,41 +1633,41 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="I13" t="n">
-        <v>4003801</v>
+        <v>4003101</v>
       </c>
       <c r="J13" t="n">
-        <v>4003801</v>
+        <v>4003101</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>难度8通关(3级)</t>
+          <t>剑与魔法通关次数(5级,合并自各难度成就)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>309001</v>
+        <v>400001</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1,10,100</t>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>900,4500,22500,</t>
+          <t>100,200,300,400,500,600,700,800,900,1000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1676,101 +1676,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="I14" t="n">
-        <v>4003901</v>
+        <v>4004001</v>
       </c>
       <c r="J14" t="n">
-        <v>4003901</v>
+        <v>4004001</v>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>难度9通关(3级)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>310001</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1,10,100</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1000,5000,25000,</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ui_achievement_clear,Achievement</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>328</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4003001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4003001</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>难度10通关(3级)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>400001</v>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>100,200,300,400,500,600,700,800,900,1000</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ui_achievement_clear,Achievement</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>401</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4004001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4004001</v>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>剑与魔法逐难度通关(10级,已通不同难度数)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_achievement_info[成就信息].xlsx
@@ -1533,12 +1533,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10,100,1000,10000,100000,1000000</t>
+          <t>10,100,1000,5000,10000,50000,100000,500000,1000000,10000000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10,50,200,500,1000,5000</t>
+          <t>10,50,200,500,1000,5000,10000,20000,50000,100000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>击杀生物(6级)</t>
+          <t>击杀生物(10级)</t>
         </is>
       </c>
     </row>
